--- a/data/supplementary_information/5.Balancing_selection_top1_regions.xlsx
+++ b/data/supplementary_information/5.Balancing_selection_top1_regions.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/subhashmahamkali/Documents/gwas_sap/data/supplementary_information/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A26E1FE-49F6-2049-B1FA-102A98CB46F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0074B0E0-A56C-C742-8CCD-A0564241E91C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="27040" windowHeight="15900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="top1_balancing_regions" sheetId="1" r:id="rId1"/>
+    <sheet name="Significant_balancing_regions" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -46,7 +46,7 @@
     <t>Improved</t>
   </si>
   <si>
-    <t>Table S. Balanced loci detected in wild, landrace, and improved sorghum groups.</t>
+    <t>Table S5. Balanced loci detected in wild, landrace, and improved sorghum groups.</t>
   </si>
 </sst>
 </file>
@@ -90,8 +90,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -401,30 +402,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+    </row>
+    <row r="2" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
     </row>
